--- a/26-10-29/exp2-gemini/Gemini实验结果02.xlsx
+++ b/26-10-29/exp2-gemini/Gemini实验结果02.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验结果" sheetId="1" r:id="Rf675c0cd53c54751"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整回复" sheetId="2" r:id="R9fb4397b53894b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验结果" sheetId="1" r:id="R43fa0537aba64bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整回复" sheetId="2" r:id="Rd6fd938278094df9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -409,7 +409,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="23" t="str">
-        <x:v>Gemini实验结果02：192个有效条件（含11条授权补测）（第01轮）</x:v>
+        <x:v>Gemini实验结果02（第01轮）</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -480,12 +480,12 @@
       <x:c r="L4" s="1"/>
       <x:c r="M4" s="1"/>
       <x:c r="O4" t="str">
-        <x:v>异常未评分不按0分处理；本次仅一轮，无同条件重复测量标准差。</x:v>
+        <x:v>本次仅一轮，无同条件重复测量标准差。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="1" t="str">
-        <x:v>2026-10-29　每档1次　每图100个目标字符　181条首次有效＋11条补测；六字号×32灰度，每条件选用一条完整有效结果。</x:v>
+        <x:v>2026-10-29　六字号×32灰度　每条件一条有效结果</x:v>
       </x:c>
       <x:c r="B5" s="1"/>
       <x:c r="C5" s="1"/>
@@ -519,7 +519,7 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="1" t="str">
-        <x:v>补测行明确标注；真实低分/0分/插入均保留。单轮无重复测量SD。</x:v>
+        <x:v>真实识读错误及多余字符均保留；单轮无重复测量标准差。</x:v>
       </x:c>
       <x:c r="B7" s="1"/>
       <x:c r="C7" s="1"/>
@@ -4578,7 +4578,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I86" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J86" s="9" t="n">
         <x:v>32</x:v>
@@ -5223,7 +5223,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I101" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J101" s="9" t="n">
         <x:v>32</x:v>
@@ -5739,7 +5739,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I113" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J113" s="9" t="n">
         <x:v>40</x:v>
@@ -5954,7 +5954,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I118" s="11" t="str">
-        <x:v>补测补齐；逐字符正确</x:v>
+        <x:v>逐字符正确</x:v>
       </x:c>
       <x:c r="J118" s="9" t="n">
         <x:v>40</x:v>
@@ -6642,7 +6642,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I134" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J134" s="9" t="n">
         <x:v>40</x:v>
@@ -7416,7 +7416,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I152" s="11" t="str">
-        <x:v>补测补齐；逐字符正确</x:v>
+        <x:v>逐字符正确</x:v>
       </x:c>
       <x:c r="J152" s="9" t="n">
         <x:v>48</x:v>
@@ -7588,7 +7588,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I156" s="11" t="str">
-        <x:v>补测补齐；逐字符正确</x:v>
+        <x:v>逐字符正确</x:v>
       </x:c>
       <x:c r="J156" s="9" t="n">
         <x:v>48</x:v>
@@ -8104,7 +8104,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I168" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J168" s="9" t="n">
         <x:v>48</x:v>
@@ -8448,7 +8448,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I176" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J176" s="9" t="n">
         <x:v>64</x:v>
@@ -9136,7 +9136,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I192" s="11" t="str">
-        <x:v>补测补齐；存在识读错误</x:v>
+        <x:v>存在识读错误</x:v>
       </x:c>
       <x:c r="J192" s="9" t="n">
         <x:v>64</x:v>
@@ -9480,7 +9480,7 @@
         <x:v>最大亮度</x:v>
       </x:c>
       <x:c r="I200" s="11" t="str">
-        <x:v>补测补齐；逐字符正确</x:v>
+        <x:v>逐字符正确</x:v>
       </x:c>
       <x:c r="J200" s="9" t="n">
         <x:v>64</x:v>
@@ -9610,7 +9610,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8dab471fb8f47bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf97534b9493444b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
